--- a/public/documents/pieces-defense/RF-quantites-anormales.xlsx
+++ b/public/documents/pieces-defense/RF-quantites-anormales.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quantites aberrantes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Suppressions &gt;= 200 EUR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Qte elevees (supprimees)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fractions = partage a N" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Notes-exemples" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,7 +60,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,382 +427,384 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Heure</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Montant saisi</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Produit (prix correct)</t>
+          <t>Montant supprime (EUR)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Prix unitaire</t>
+          <t>Qte (ordre de grandeur, ~18 EUR/plat)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Quantité saisie</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Supprimée le jour même</t>
+          <t>Statut</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>2022-07-26</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>18:51</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>68993.10000000001</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PICHET MOULIN A VENT</t>
-        </is>
-      </c>
       <c r="E2" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2518</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>OUI</t>
+        <v>3800</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Entrecôte grillée</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>44955</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3467</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>2500</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Crémeux du Jura</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19600</v>
       </c>
       <c r="E4" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3616</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PEUTE</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4455</v>
       </c>
       <c r="E5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3876</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>44955</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Macvin du Jura</t>
-        </is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>810</v>
       </c>
       <c r="E6" t="n">
         <v>45</v>
       </c>
-      <c r="F6" t="n">
-        <v>999</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>OUI</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PICHET GEWURZTRAMINE</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>481</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1665</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complète</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>409.2</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2997</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VALENTINE</t>
-        </is>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>408</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4050</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>19600</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Menu du jour</t>
-        </is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>243.4</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" t="n">
-        <v>196</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>OUI</t>
+        <v>15</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>H.C.B BEAUNE BTL</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>239.2</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
-      </c>
-      <c r="F11" t="n">
-        <v>400</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Crémeux du Jura</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>204</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" t="n">
-        <v>490</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Alsace Gewurztramine</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>204</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F13" t="n">
-        <v>560</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4455</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Champagne</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>81</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Macvin du Jura</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>45</v>
-      </c>
-      <c r="F15" t="n">
-        <v>99</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ENTRECOTE MORILLES</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>128</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Crémant du Jura</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="F17" t="n">
-        <v>149</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Supprime (DEL)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -814,374 +817,1611 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Exercice</t>
+          <t>Partage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fraction unitaire</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Heure</t>
+          <t>Fractions observees</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Montant supprimé (€)</t>
+          <t>Lignes</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Quantité aberrante ? (prix×qté)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supprimée le jour même</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Partage a 2 convives</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>0,5, 1,5, 2,5, 3,5, 4,5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68993.10000000001</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PICHET MOULIN A VENT : 27.4 × 2518</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>9804</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>Partage a 3 convives</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>0,33, 0,34, 0,66, 0,67, 1,33, 1,67, 3,33</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44955</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Macvin du Jura : 45.0 × 999</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>502</v>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Partage a 4 convives</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>0,25, 0,75, 1,25, 1,75, 2,25, 5,25, 6,75</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19600</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Menu du jour : 100.0 × 196</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>340</v>
+      </c>
+      <c r="E4" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>Partage a 5 convives</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>0,2, 0,4, 0,6, 0,8, 1,6, 2,4, 3,2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4455</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Champagne : 55.0 × 81</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>208</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>Partage a 6 convives</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>0,16, 0,17, 0,83</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Partage a 7 convives</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>0,14, 0,15, 0,28, 0,29, 0,43</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>159</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>Partage a 12 convives</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>409.2</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OUI</t>
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure / note</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quantite</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prix unitaire</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14/04/2022 note 13 (exemple du fisc)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TOTAL 26,45 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cidre Bouché Brut</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14,00 €</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FRELEE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18,60 €</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9,30 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CABRICHOU</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15,90 €</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,95 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Somme lignes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26,45 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14/04/2022 note 14 (la moitie manquante)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TOTAL 26,45 €</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>Cidre Bouché Brut</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>408</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OUI</t>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>14,00 €</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,00 €</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>243.4</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OUI</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>FRELEE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>239.2</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OUI</t>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>18,60 €</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9,30 €</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>CABRICHOU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>204</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OUI</t>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15,90 €</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,95 €</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>204</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OUI</t>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Somme lignes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26,45 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023-03-04 note 28 (partage a 5)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TOTAL 38,54 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gewurztraminer Le ve</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7,00 €</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Whisky L.J (4cl)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5,80 €</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1,16 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sirop à l'eau</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0,44 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pinte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7,80 €</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1,56 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MACHON GOURMET</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>25,00 €</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>POULET JURASSIENNE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>18,60 €</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fondue Jurassienne</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16,90 €</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6,76 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>POMMES FRITES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1,56 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Assortiment charcute</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8,90 €</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1,78 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pichet 50cl vin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9,80 €</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1,96 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Crêpe sucrée</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2,90 €</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1,16 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>La</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8,50 €</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1,70 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ré</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7,00 €</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1,40 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TENDRESSE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0,78 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1,76 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Somme lignes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>38,54 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-03-10 note 15 (partage a 7)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TOTAL 27,54 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Picon bière</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4,50 €</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1,26 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kir Bourgogne</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4,20 €</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1,76 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jus de Fruit</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0,55 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>La Vouivre</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5,20 €</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TANTELIN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>16,40 €</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2,30 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Galette nature</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sauce Morilles</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14,90 €</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2,09 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pommes de Terre</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3,20 €</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Champignons frais</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3,20 €</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0,45 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Œuf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0,90 €</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0,13 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cancoillotte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0,55 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Comté</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4,00 €</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0,56 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BARBEULENET</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13,90 €</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1,95 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TRUITE PESTO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>16,90 €</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2,37 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BURGER COMTOIS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>19,00 €</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2,66 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cidre Bouché Brut</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>14,00 €</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1,96 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Crepe Chocolat</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4,70 €</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0,66 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GLACE 2 BOULES</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3,90 €</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1,09 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chantilly</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1,80 €</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0,25 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DOUCEUR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8,70 €</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1,22 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FLIRT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8,10 €</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1,13 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CUPIDON</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>7,50 €</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1,05 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2,20 €</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0,62 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Somme lignes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>27,88 €</t>
         </is>
       </c>
     </row>
